--- a/weeks/◆ 2026년 09월 4주 편성표 (0921 ~ 0927).xlsx
+++ b/weeks/◆ 2026년 09월 4주 편성표 (0921 ~ 0927).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="40">
+  <fonts count="39">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -254,12 +254,6 @@
       <color rgb="00333333"/>
       <u val="none"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -378,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -503,13 +497,10 @@
     <xf numFmtId="49" fontId="36" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="37" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="38" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,48 +517,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -614,7 +605,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -966,7 +957,7 @@
       </c>
       <c r="S8" s="30" t="inlineStr">
         <is>
-          <t>컬럼비아 26FW 론칭</t>
+          <t>헤드 FW 에어 워킹화</t>
         </is>
       </c>
       <c r="T8" s="25"/>
@@ -999,7 +990,7 @@
       <c r="Z8" s="25"/>
       <c r="AA8" s="32" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AB8" s="33" t="inlineStr">
@@ -1014,12 +1005,12 @@
       </c>
       <c r="AD8" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>편성전략</t>
         </is>
       </c>
       <c r="AE8" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>위프 탈취제</t>
         </is>
       </c>
       <c r="AF8" s="25"/>
@@ -1189,27 +1180,27 @@
       <c r="Z9" s="25"/>
       <c r="AA9" s="32" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AB9" s="33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AC9" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD9" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>'건강식품1'</t>
         </is>
       </c>
       <c r="AE9" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
         </is>
       </c>
       <c r="AF9" s="25"/>
@@ -1311,7 +1302,7 @@
       </c>
       <c r="K10" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="L10" s="30" t="inlineStr">
@@ -1321,7 +1312,7 @@
       </c>
       <c r="M10" s="30" t="inlineStr">
         <is>
-          <t>(한가위)슈올즈 포브</t>
+          <t>스케쳐스 코지핏 컨투어폼 워킹화</t>
         </is>
       </c>
       <c r="N10" s="25"/>
@@ -1378,9 +1369,9 @@
         </is>
       </c>
       <c r="Z10" s="25"/>
-      <c r="AA10" s="29" t="inlineStr">
-        <is>
-          <t>07:20</t>
+      <c r="AA10" s="32" t="inlineStr">
+        <is>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AB10" s="33" t="inlineStr">
@@ -1395,12 +1386,12 @@
       </c>
       <c r="AD10" s="34" t="inlineStr">
         <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="AE10" s="39" t="inlineStr">
-        <is>
-          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
+          <t>편성전략</t>
+        </is>
+      </c>
+      <c r="AE10" s="35" t="inlineStr">
+        <is>
+          <t>타파웨어 원터치</t>
         </is>
       </c>
       <c r="AF10" s="25"/>
@@ -1522,7 +1513,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -1537,7 +1528,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="S11" s="30" t="inlineStr">
+      <c r="S11" s="39" t="inlineStr">
         <is>
           <t>한가위-이상봉 보니타 숄더백</t>
         </is>
@@ -1572,7 +1563,7 @@
       <c r="Z11" s="25"/>
       <c r="AA11" s="32" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AB11" s="33" t="inlineStr">
@@ -1582,17 +1573,17 @@
       </c>
       <c r="AC11" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AD11" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>편성전략</t>
         </is>
       </c>
       <c r="AE11" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>머티리얼랩</t>
         </is>
       </c>
       <c r="AF11" s="25"/>
@@ -1691,20 +1682,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K12" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="L12" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>P.D.Lab</t>
         </is>
       </c>
       <c r="M12" s="30" t="inlineStr">
         <is>
-          <t>가히 캐비어밤</t>
+          <t>알레보 클리어 냄비</t>
         </is>
       </c>
       <c r="N12" s="25"/>
@@ -1713,7 +1703,7 @@
           <t>09:25</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1728,7 +1718,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="39" t="inlineStr">
         <is>
           <t>디아루체 울 100 브이넥 레이어드 니트</t>
         </is>
@@ -1762,23 +1752,27 @@
       <c r="Z12" s="25"/>
       <c r="AA12" s="32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AB12" s="33" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AC12" s="24"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC12" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
       <c r="AD12" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>편성전략</t>
         </is>
       </c>
       <c r="AE12" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>한국중앙금거래소 24K주얼리</t>
         </is>
       </c>
       <c r="AF12" s="25"/>
@@ -1911,12 +1905,12 @@
       </c>
       <c r="R13" s="30" t="inlineStr">
         <is>
-          <t>P.D.Lab</t>
+          <t>'패션1Lab'</t>
         </is>
       </c>
       <c r="S13" s="30" t="inlineStr">
         <is>
-          <t>알레보 밥용기</t>
+          <t>한가위- 프리마클라쎄 26fw</t>
         </is>
       </c>
       <c r="T13" s="25"/>
@@ -1930,25 +1924,26 @@
           <t>70</t>
         </is>
       </c>
-      <c r="W13" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W13" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X13" s="30" t="inlineStr">
         <is>
-          <t>'패션1Lab'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="Y13" s="30" t="inlineStr">
         <is>
-          <t>한가위- 프리마클라쎄 26fw</t>
+          <t>가히 캐비어밤</t>
         </is>
       </c>
       <c r="Z13" s="25"/>
       <c r="AA13" s="32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AB13" s="33" t="inlineStr">
@@ -1958,17 +1953,17 @@
       </c>
       <c r="AC13" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD13" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>편성전략</t>
         </is>
       </c>
       <c r="AE13" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>프리마클라쎄</t>
         </is>
       </c>
       <c r="AF13" s="25"/>
@@ -2110,7 +2105,7 @@
         </is>
       </c>
       <c r="T14" s="25"/>
-      <c r="U14" s="32" t="inlineStr">
+      <c r="U14" s="29" t="inlineStr">
         <is>
           <t>11:35</t>
         </is>
@@ -2120,45 +2115,46 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W14" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W14" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X14" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="Y14" s="42" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="Y14" s="30" t="inlineStr">
+        <is>
+          <t>베스티안 SP MD 크림</t>
         </is>
       </c>
       <c r="Z14" s="25"/>
       <c r="AA14" s="32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AB14" s="33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AC14" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AD14" s="34" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>편성전략</t>
         </is>
       </c>
       <c r="AE14" s="35" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
+          <t>애비스 칫솔</t>
         </is>
       </c>
       <c r="AF14" s="25"/>
@@ -2182,7 +2178,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AK14" s="43" t="inlineStr">
+      <c r="AK14" s="42" t="inlineStr">
         <is>
           <t>프라다_숄더백</t>
         </is>
@@ -2286,7 +2282,7 @@
       </c>
       <c r="Q15" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="R15" s="30" t="inlineStr">
@@ -2296,7 +2292,7 @@
       </c>
       <c r="S15" s="30" t="inlineStr">
         <is>
-          <t>오토드 진공스팀다리미</t>
+          <t>(재)해즈픽 칫솔</t>
         </is>
       </c>
       <c r="T15" s="25"/>
@@ -2326,29 +2322,29 @@
         </is>
       </c>
       <c r="Z15" s="25"/>
-      <c r="AA15" s="32" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AB15" s="33" t="inlineStr">
-        <is>
-          <t>50</t>
+      <c r="AA15" s="29" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AB15" s="24" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="AC15" s="24" t="inlineStr">
         <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="AD15" s="34" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE15" s="35" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AD15" s="30" t="inlineStr">
+        <is>
+          <t>'일반식품2'</t>
+        </is>
+      </c>
+      <c r="AE15" s="43" t="inlineStr">
+        <is>
+          <t>(한가위)(재)난각 1번 40구</t>
         </is>
       </c>
       <c r="AF15" s="25"/>
@@ -2372,7 +2368,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AK15" s="43" t="inlineStr">
+      <c r="AK15" s="42" t="inlineStr">
         <is>
           <t>구찌_숄더백</t>
         </is>
@@ -2499,9 +2495,10 @@
           <t>50</t>
         </is>
       </c>
-      <c r="W16" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W16" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X16" s="30" t="inlineStr">
@@ -2511,33 +2508,34 @@
       </c>
       <c r="Y16" s="30" t="inlineStr">
         <is>
-          <t>해즈픽 칫솔</t>
+          <t>솔솔랩 국산 편백베개</t>
         </is>
       </c>
       <c r="Z16" s="25"/>
       <c r="AA16" s="29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AB16" s="24" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AC16" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AD16" s="30" t="inlineStr">
-        <is>
-          <t>'일반식품2'</t>
-        </is>
-      </c>
-      <c r="AE16" s="44" t="inlineStr">
-        <is>
-          <t>(한가위)(재)난각 1번 40구</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AC16" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
+        </is>
+      </c>
+      <c r="AD16" s="34" t="inlineStr">
+        <is>
+          <t>'패션1Lab'</t>
+        </is>
+      </c>
+      <c r="AE16" s="43" t="inlineStr">
+        <is>
+          <t>플레이백 니트 外</t>
         </is>
       </c>
       <c r="AF16" s="25"/>
@@ -2667,17 +2665,17 @@
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="R17" s="30" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="S17" s="30" t="inlineStr">
         <is>
-          <t>리더스 아이크림</t>
+          <t>S.A.F 바디워시</t>
         </is>
       </c>
       <c r="T17" s="25"/>
@@ -2710,7 +2708,7 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AB17" s="24" t="inlineStr">
@@ -2718,20 +2716,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="AC17" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
-      <c r="AD17" s="34" t="inlineStr">
-        <is>
-          <t>'패션1Lab'</t>
-        </is>
-      </c>
-      <c r="AE17" s="44" t="inlineStr">
-        <is>
-          <t>플레이백 니트 外</t>
+      <c r="AC17" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="AD17" s="30" t="inlineStr">
+        <is>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="AE17" s="43" t="inlineStr">
+        <is>
+          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
         </is>
       </c>
       <c r="AF17" s="25"/>
@@ -2904,7 +2901,7 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AB18" s="24" t="inlineStr">
@@ -2912,19 +2909,20 @@
           <t>50</t>
         </is>
       </c>
-      <c r="AC18" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
+      <c r="AC18" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AD18" s="30" t="inlineStr">
         <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="AE18" s="44" t="inlineStr">
-        <is>
-          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AE18" s="43" t="inlineStr">
+        <is>
+          <t>센스락 진공포장기</t>
         </is>
       </c>
       <c r="AF18" s="25"/>
@@ -3094,7 +3092,7 @@
       <c r="Z19" s="25"/>
       <c r="AA19" s="29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AB19" s="24" t="inlineStr">
@@ -3102,72 +3100,71 @@
           <t>50</t>
         </is>
       </c>
-      <c r="AC19" s="31" t="inlineStr">
+      <c r="AC19" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="AD19" s="30" t="inlineStr">
+        <is>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="AE19" s="43" t="inlineStr">
+        <is>
+          <t>뉴케어 구수한맛 밸런스업</t>
+        </is>
+      </c>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="29" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AH19" s="33" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AI19" s="31" t="inlineStr">
         <is>
           <t>대
 수</t>
         </is>
       </c>
-      <c r="AD19" s="30" t="inlineStr">
+      <c r="AJ19" s="30" t="inlineStr">
         <is>
           <t>'가전'</t>
         </is>
       </c>
-      <c r="AE19" s="44" t="inlineStr">
-        <is>
-          <t>LG TV</t>
-        </is>
-      </c>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="29" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AH19" s="33" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AI19" s="31" t="inlineStr">
+      <c r="AK19" s="41" t="inlineStr">
+        <is>
+          <t>LG 건조기</t>
+        </is>
+      </c>
+      <c r="AL19" s="25"/>
+      <c r="AM19" s="29" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AN19" s="37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AO19" s="31" t="inlineStr">
         <is>
           <t>대
 수</t>
         </is>
       </c>
-      <c r="AJ19" s="30" t="inlineStr">
-        <is>
-          <t>'가전'</t>
-        </is>
-      </c>
-      <c r="AK19" s="41" t="inlineStr">
-        <is>
-          <t>LG 건조기</t>
-        </is>
-      </c>
-      <c r="AL19" s="25"/>
-      <c r="AM19" s="29" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="AN19" s="37" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AO19" s="31" t="inlineStr">
-        <is>
-          <t>대
-수</t>
-        </is>
-      </c>
       <c r="AP19" s="30" t="inlineStr">
         <is>
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AQ19" s="43" t="inlineStr">
+      <c r="AQ19" s="42" t="inlineStr">
         <is>
           <t>노랑풍선 호주</t>
         </is>
@@ -3198,12 +3195,12 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>'가전'</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>테팔 그릴</t>
+          <t>삼성로봇청소기</t>
         </is>
       </c>
       <c r="H20" s="25"/>
@@ -3219,96 +3216,97 @@
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
+          <t>대
+수</t>
+        </is>
+      </c>
+      <c r="L20" s="30" t="inlineStr">
+        <is>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="M20" s="30" t="inlineStr">
+        <is>
+          <t>LG TV</t>
+        </is>
+      </c>
+      <c r="N20" s="25"/>
+      <c r="O20" s="29" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="P20" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q20" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="R20" s="30" t="inlineStr">
+        <is>
+          <t>'건강식품1'</t>
+        </is>
+      </c>
+      <c r="S20" s="30" t="inlineStr">
+        <is>
+          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
+        </is>
+      </c>
+      <c r="T20" s="25"/>
+      <c r="U20" s="29" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W20" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="X20" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="Y20" s="30" t="inlineStr">
+        <is>
+          <t>셀폰즈 녹는실 앰플</t>
+        </is>
+      </c>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="29" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AB20" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AC20" s="31" t="inlineStr">
+        <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>'리빙'</t>
-        </is>
-      </c>
-      <c r="M20" s="30" t="inlineStr">
-        <is>
-          <t>솔솔랩 국산 편백베개</t>
-        </is>
-      </c>
-      <c r="N20" s="25"/>
-      <c r="O20" s="29" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="P20" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="Q20" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="R20" s="30" t="inlineStr">
-        <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="S20" s="30" t="inlineStr">
-        <is>
-          <t>(한가위)(재)비에날씬 재방(10%할인)</t>
-        </is>
-      </c>
-      <c r="T20" s="25"/>
-      <c r="U20" s="29" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W20" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="X20" s="30" t="inlineStr">
-        <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="Y20" s="30" t="inlineStr">
-        <is>
-          <t>셀폰즈 녹는실 앰플</t>
-        </is>
-      </c>
-      <c r="Z20" s="25"/>
-      <c r="AA20" s="29" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AB20" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AC20" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
       <c r="AD20" s="30" t="inlineStr">
         <is>
-          <t>'건강식품1'</t>
-        </is>
-      </c>
-      <c r="AE20" s="44" t="inlineStr">
-        <is>
-          <t>뉴케어 구수한맛 밸런스업</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="AE20" s="43" t="inlineStr">
+        <is>
+          <t>한경희 스팀청소기</t>
         </is>
       </c>
       <c r="AF20" s="25"/>
@@ -3478,7 +3476,7 @@
       <c r="Z21" s="25"/>
       <c r="AA21" s="29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AB21" s="24" t="inlineStr">
@@ -3494,12 +3492,12 @@
       </c>
       <c r="AD21" s="30" t="inlineStr">
         <is>
-          <t>'가전'</t>
-        </is>
-      </c>
-      <c r="AE21" s="44" t="inlineStr">
-        <is>
-          <t>한경희 스팀청소기</t>
+          <t>'일반렌탈'</t>
+        </is>
+      </c>
+      <c r="AE21" s="40" t="inlineStr">
+        <is>
+          <t>더케이예다함 상조</t>
         </is>
       </c>
       <c r="AF21" s="25"/>
@@ -3570,154 +3568,152 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>'액티브라이프'</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(한가위)(재)황금오징어 </t>
+        </is>
+      </c>
+      <c r="H22" s="25"/>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="L22" s="30" t="inlineStr">
+        <is>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M22" s="40" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
+        </is>
+      </c>
+      <c r="N22" s="25"/>
+      <c r="O22" s="29" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="P22" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q22" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="R22" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="S22" s="30" t="inlineStr">
+        <is>
+          <t>AHC 아이크림</t>
+        </is>
+      </c>
+      <c r="T22" s="25"/>
+      <c r="U22" s="29" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W22" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
+        </is>
+      </c>
+      <c r="X22" s="30" t="inlineStr">
+        <is>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="Y22" s="30" t="inlineStr">
+        <is>
+          <t>테이핑테크 더블슬개건 무릎보호대</t>
+        </is>
+      </c>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="29" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AB22" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AC22" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="AD22" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="AE22" s="43" t="inlineStr">
+        <is>
+          <t>한가위-[재]보로탈코 바디크림</t>
+        </is>
+      </c>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="29" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AH22" s="37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AI22" s="31" t="inlineStr">
         <is>
           <t>대
 수</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
-        <is>
-          <t>'건강식품2'</t>
-        </is>
-      </c>
-      <c r="G22" s="30" t="inlineStr">
-        <is>
-          <t>종근당건강 당케어프로</t>
-        </is>
-      </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="29" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="J22" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M22" s="40" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
-        </is>
-      </c>
-      <c r="N22" s="25"/>
-      <c r="O22" s="29" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="P22" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q22" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="R22" s="30" t="inlineStr">
-        <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="S22" s="30" t="inlineStr">
-        <is>
-          <t>라피타 IPL 멜라클린</t>
-        </is>
-      </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="29" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W22" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
-      <c r="X22" s="30" t="inlineStr">
-        <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="Y22" s="30" t="inlineStr">
-        <is>
-          <t>센스락 진공포장기</t>
-        </is>
-      </c>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="29" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AB22" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AC22" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
-      <c r="AD22" s="30" t="inlineStr">
-        <is>
-          <t>'일반렌탈'</t>
-        </is>
-      </c>
-      <c r="AE22" s="40" t="inlineStr">
-        <is>
-          <t>더케이예다함 상조</t>
-        </is>
-      </c>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="29" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
-      <c r="AH22" s="37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AI22" s="31" t="inlineStr">
-        <is>
-          <t>대
-수</t>
-        </is>
-      </c>
       <c r="AJ22" s="30" t="inlineStr">
         <is>
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AK22" s="43" t="inlineStr">
+      <c r="AK22" s="42" t="inlineStr">
         <is>
           <t>롯데관광 동남아</t>
         </is>
@@ -3759,27 +3755,28 @@
       <c r="B23" s="25"/>
       <c r="C23" s="29" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="F23" s="30" t="inlineStr">
         <is>
-          <t>'액티브라이프'</t>
+          <t>'건강식품2'</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">(한가위)(재)황금오징어 </t>
+          <t>종근당건강 당케어프로</t>
         </is>
       </c>
       <c r="H23" s="25"/>
@@ -3822,70 +3819,71 @@
       </c>
       <c r="Q23" s="31" t="inlineStr">
         <is>
+          <t>대
+수</t>
+        </is>
+      </c>
+      <c r="R23" s="30" t="inlineStr">
+        <is>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="S23" s="30" t="inlineStr">
+        <is>
+          <t>락앤락 머스트픽</t>
+        </is>
+      </c>
+      <c r="T23" s="25"/>
+      <c r="U23" s="29" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W23" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="X23" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="Y23" s="30" t="inlineStr">
+        <is>
+          <t>한가위-[재]보로탈코 바디크림</t>
+        </is>
+      </c>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AB23" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC23" s="31" t="inlineStr">
+        <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
-        <is>
-          <t>'리빙'</t>
-        </is>
-      </c>
-      <c r="S23" s="30" t="inlineStr">
-        <is>
-          <t>비리빙 압축파우치</t>
-        </is>
-      </c>
-      <c r="T23" s="25"/>
-      <c r="U23" s="29" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W23" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="X23" s="30" t="inlineStr">
-        <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="Y23" s="30" t="inlineStr">
-        <is>
-          <t>한가위-[재]보로탈코 바디크림</t>
-        </is>
-      </c>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="29" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AB23" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AC23" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
       <c r="AD23" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
-        </is>
-      </c>
-      <c r="AE23" s="44" t="inlineStr">
-        <is>
-          <t>한가위-[재]보로탈코 바디크림</t>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AE23" s="43" t="inlineStr">
+        <is>
+          <t>로렌힐스 싱크볼</t>
         </is>
       </c>
       <c r="AF23" s="25"/>
@@ -4038,30 +4036,31 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W24" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W24" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X24" s="30" t="inlineStr">
         <is>
-          <t>'패션4Lab'</t>
+          <t>'리빙'</t>
         </is>
       </c>
       <c r="Y24" s="30" t="inlineStr">
         <is>
-          <t>정호진 원데이 (오후)</t>
+          <t>비리빙 압축파우치</t>
         </is>
       </c>
       <c r="Z24" s="25"/>
       <c r="AA24" s="29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AB24" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AC24" s="31" t="inlineStr">
@@ -4072,12 +4071,12 @@
       </c>
       <c r="AD24" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="AE24" s="44" t="inlineStr">
-        <is>
-          <t>로렌힐스 싱크볼</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AE24" s="43" t="inlineStr">
+        <is>
+          <t>스노락 코골이완화기기+살균기구성</t>
         </is>
       </c>
       <c r="AF24" s="25"/>
@@ -4104,7 +4103,7 @@
       </c>
       <c r="AK24" s="30" t="inlineStr">
         <is>
-          <t>사업부-씨드비 물염색</t>
+          <t>팀-씨드비 물염색</t>
         </is>
       </c>
       <c r="AL24" s="25"/>
@@ -4118,20 +4117,19 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO24" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AP24" s="30" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
+          <t>'리빙'</t>
         </is>
       </c>
       <c r="AQ24" s="30" t="inlineStr">
         <is>
-          <t>베스티안 MD크림</t>
+          <t>일월 온열매트</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4147,7 @@
       </c>
       <c r="D25" s="37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -4159,12 +4157,12 @@
       </c>
       <c r="F25" s="30" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
+          <t>'패션2Lab'</t>
         </is>
       </c>
       <c r="G25" s="38" t="inlineStr">
         <is>
-          <t>머티리얼랩 퓨어 캐시미어100 헨리넥 니트 外</t>
+          <t>라이317레이어링티셔츠2종</t>
         </is>
       </c>
       <c r="H25" s="25"/>
@@ -4206,72 +4204,72 @@
       </c>
       <c r="Q25" s="31" t="inlineStr">
         <is>
+          <t>대
+수</t>
+        </is>
+      </c>
+      <c r="R25" s="30" t="inlineStr">
+        <is>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="S25" s="30" t="inlineStr">
+        <is>
+          <t>AHC 아이크림</t>
+        </is>
+      </c>
+      <c r="T25" s="25"/>
+      <c r="U25" s="29" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="W25" s="31" t="inlineStr">
+        <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="R25" s="30" t="inlineStr">
-        <is>
-          <t>'리빙'</t>
-        </is>
-      </c>
-      <c r="S25" s="30" t="inlineStr">
-        <is>
-          <t>스노락 코골이완화기기+살균기구성</t>
-        </is>
-      </c>
-      <c r="T25" s="25"/>
-      <c r="U25" s="29" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="W25" s="31" t="inlineStr">
+      <c r="X25" s="30" t="inlineStr">
+        <is>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="Y25" s="30" t="inlineStr">
+        <is>
+          <t>한국중앙금거래소 24K</t>
+        </is>
+      </c>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="29" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AB25" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC25" s="31" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="X25" s="30" t="inlineStr">
-        <is>
-          <t>'주얼리'</t>
-        </is>
-      </c>
-      <c r="Y25" s="30" t="inlineStr">
-        <is>
-          <t>한민금거래소 18k</t>
-        </is>
-      </c>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="29" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AB25" s="24" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AC25" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
       <c r="AD25" s="30" t="inlineStr">
         <is>
-          <t>'뷰티브랜드'</t>
-        </is>
-      </c>
-      <c r="AE25" s="44" t="inlineStr">
-        <is>
-          <t>라비오라 워시오프팩</t>
+          <t>'국내여행'</t>
+        </is>
+      </c>
+      <c r="AE25" s="43" t="inlineStr">
+        <is>
+          <t>설악 오션투유</t>
         </is>
       </c>
       <c r="AF25" s="25"/>
@@ -4337,12 +4335,12 @@
       <c r="B26" s="25"/>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="37" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -4352,12 +4350,12 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
+          <t>'패션3Lab'</t>
         </is>
       </c>
       <c r="G26" s="38" t="inlineStr">
         <is>
-          <t>라이317레이어링티셔츠2종</t>
+          <t>머티리얼랩 퓨어 캐시미어100 헨리넥 니트 外</t>
         </is>
       </c>
       <c r="H26" s="25"/>
@@ -4443,7 +4441,7 @@
       <c r="Z26" s="25"/>
       <c r="AA26" s="29" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AB26" s="24" t="inlineStr">
@@ -4459,12 +4457,12 @@
       </c>
       <c r="AD26" s="30" t="inlineStr">
         <is>
-          <t>'국내여행'</t>
-        </is>
-      </c>
-      <c r="AE26" s="44" t="inlineStr">
-        <is>
-          <t>설악 오션투유</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="AE26" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디아넬로 24K </t>
         </is>
       </c>
       <c r="AF26" s="25"/>
@@ -4488,7 +4486,7 @@
           <t>'뷰티2'</t>
         </is>
       </c>
-      <c r="AK26" s="43" t="inlineStr">
+      <c r="AK26" s="42" t="inlineStr">
         <is>
           <t>제우스 바디 디바이스</t>
         </is>
@@ -4511,29 +4509,29 @@
         </is>
       </c>
       <c r="B27" s="25"/>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>21:15</t>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>21:10</t>
         </is>
       </c>
       <c r="D27" s="37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G27" s="42" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="G27" s="38" t="inlineStr">
+        <is>
+          <t>페라가모 시계</t>
         </is>
       </c>
       <c r="H27" s="25"/>
@@ -4619,28 +4617,27 @@
       <c r="Z27" s="25"/>
       <c r="AA27" s="29" t="inlineStr">
         <is>
-          <t>21:40</t>
-        </is>
-      </c>
-      <c r="AB27" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AC27" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB27" s="37" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AC27" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AD27" s="30" t="inlineStr">
         <is>
-          <t>'주얼리'</t>
-        </is>
-      </c>
-      <c r="AE27" s="44" t="inlineStr">
-        <is>
-          <t>한국중앙금거래소 24K</t>
+          <t>'노블레스'</t>
+        </is>
+      </c>
+      <c r="AE27" s="42" t="inlineStr">
+        <is>
+          <t>버버리_토트백</t>
         </is>
       </c>
       <c r="AF27" s="25"/>
@@ -4763,7 +4760,7 @@
       </c>
       <c r="S28" s="30" t="inlineStr">
         <is>
-          <t>더앤리조트</t>
+          <t>엘시티 해운대</t>
         </is>
       </c>
       <c r="T28" s="25"/>
@@ -4795,27 +4792,27 @@
       <c r="Z28" s="25"/>
       <c r="AA28" s="29" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AB28" s="37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AC28" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD28" s="30" t="inlineStr">
         <is>
-          <t>'노블레스'</t>
-        </is>
-      </c>
-      <c r="AE28" s="43" t="inlineStr">
-        <is>
-          <t>버버리_토트백</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="AE28" s="42" t="inlineStr">
+        <is>
+          <t>MBB 백</t>
         </is>
       </c>
       <c r="AF28" s="25"/>
@@ -4873,19 +4870,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'가전'</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
         <is>
-          <t>위프 고체탈취제</t>
+          <t>다이슨 에어스무스</t>
         </is>
       </c>
       <c r="H29" s="25"/>
@@ -4968,29 +4966,29 @@
         </is>
       </c>
       <c r="Z29" s="25"/>
-      <c r="AA29" s="32" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
-      <c r="AB29" s="37" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="AA29" s="29" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AB29" s="24" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
       <c r="AC29" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AD29" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE29" s="35" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>심야재방</t>
+        </is>
+      </c>
+      <c r="AE29" s="43" t="inlineStr">
+        <is>
+          <t>다시보는 인기상품(재)(ZONE a.m.)</t>
         </is>
       </c>
       <c r="AF29" s="25"/>
@@ -5090,7 +5088,7 @@
       </c>
       <c r="V30" s="24" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>320</t>
         </is>
       </c>
       <c r="W30" s="24" t="inlineStr">
@@ -5111,29 +5109,13 @@
       <c r="Z30" s="25"/>
       <c r="AA30" s="29" t="inlineStr">
         <is>
-          <t>01:10</t>
-        </is>
-      </c>
-      <c r="AB30" s="24" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="AC30" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AD30" s="30" t="inlineStr">
-        <is>
-          <t>심야재방</t>
-        </is>
-      </c>
-      <c r="AE30" s="44" t="inlineStr">
-        <is>
-          <t>다시보는 인기상품(재)(ZONE a.m.)</t>
-        </is>
-      </c>
+          <t>__:__</t>
+        </is>
+      </c>
+      <c r="AB30" s="24"/>
+      <c r="AC30" s="24"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="43"/>
       <c r="AF30" s="25"/>
       <c r="AG30" s="29" t="inlineStr">
         <is>
@@ -5226,7 +5208,7 @@
       <c r="AB31" s="24"/>
       <c r="AC31" s="24"/>
       <c r="AD31" s="30"/>
-      <c r="AE31" s="44"/>
+      <c r="AE31" s="43"/>
       <c r="AF31" s="25"/>
       <c r="AG31" s="29" t="inlineStr">
         <is>
@@ -5319,7 +5301,7 @@
       <c r="AB32" s="24"/>
       <c r="AC32" s="24"/>
       <c r="AD32" s="30"/>
-      <c r="AE32" s="44"/>
+      <c r="AE32" s="43"/>
       <c r="AF32" s="25"/>
       <c r="AG32" s="29" t="inlineStr">
         <is>
@@ -5412,7 +5394,7 @@
       <c r="AB33" s="24"/>
       <c r="AC33" s="24"/>
       <c r="AD33" s="30"/>
-      <c r="AE33" s="44"/>
+      <c r="AE33" s="43"/>
       <c r="AF33" s="25"/>
       <c r="AG33" s="29" t="inlineStr">
         <is>
@@ -5489,7 +5471,7 @@
       <c r="AB34" s="24"/>
       <c r="AC34" s="24"/>
       <c r="AD34" s="30"/>
-      <c r="AE34" s="44"/>
+      <c r="AE34" s="43"/>
       <c r="AF34" s="25"/>
       <c r="AG34" s="29" t="inlineStr">
         <is>
@@ -5566,7 +5548,7 @@
       <c r="AB35" s="24"/>
       <c r="AC35" s="24"/>
       <c r="AD35" s="30"/>
-      <c r="AE35" s="44"/>
+      <c r="AE35" s="43"/>
       <c r="AF35" s="25"/>
       <c r="AG35" s="29" t="inlineStr">
         <is>
@@ -5643,7 +5625,7 @@
       <c r="AB36" s="24"/>
       <c r="AC36" s="24"/>
       <c r="AD36" s="30"/>
-      <c r="AE36" s="44"/>
+      <c r="AE36" s="43"/>
       <c r="AF36" s="25"/>
       <c r="AG36" s="29" t="inlineStr">
         <is>
@@ -5720,7 +5702,7 @@
       <c r="AB37" s="24"/>
       <c r="AC37" s="24"/>
       <c r="AD37" s="30"/>
-      <c r="AE37" s="44"/>
+      <c r="AE37" s="43"/>
       <c r="AF37" s="25"/>
       <c r="AG37" s="29" t="inlineStr">
         <is>
@@ -5797,7 +5779,7 @@
       <c r="AB38" s="24"/>
       <c r="AC38" s="24"/>
       <c r="AD38" s="30"/>
-      <c r="AE38" s="44"/>
+      <c r="AE38" s="43"/>
       <c r="AF38" s="25"/>
       <c r="AG38" s="29" t="inlineStr">
         <is>
@@ -5874,7 +5856,7 @@
       <c r="AB39" s="24"/>
       <c r="AC39" s="24"/>
       <c r="AD39" s="30"/>
-      <c r="AE39" s="44"/>
+      <c r="AE39" s="43"/>
       <c r="AF39" s="25"/>
       <c r="AG39" s="29" t="inlineStr">
         <is>
@@ -5951,7 +5933,7 @@
       <c r="AB40" s="24"/>
       <c r="AC40" s="24"/>
       <c r="AD40" s="30"/>
-      <c r="AE40" s="44"/>
+      <c r="AE40" s="43"/>
       <c r="AF40" s="25"/>
       <c r="AG40" s="29" t="inlineStr">
         <is>
@@ -6028,7 +6010,7 @@
       <c r="AB41" s="24"/>
       <c r="AC41" s="24"/>
       <c r="AD41" s="30"/>
-      <c r="AE41" s="44"/>
+      <c r="AE41" s="43"/>
       <c r="AF41" s="25"/>
       <c r="AG41" s="29" t="inlineStr">
         <is>
@@ -6105,7 +6087,7 @@
       <c r="AB42" s="24"/>
       <c r="AC42" s="24"/>
       <c r="AD42" s="30"/>
-      <c r="AE42" s="44"/>
+      <c r="AE42" s="43"/>
       <c r="AF42" s="25"/>
       <c r="AG42" s="29" t="inlineStr">
         <is>
@@ -6182,7 +6164,7 @@
       <c r="AB43" s="24"/>
       <c r="AC43" s="24"/>
       <c r="AD43" s="30"/>
-      <c r="AE43" s="44"/>
+      <c r="AE43" s="43"/>
       <c r="AF43" s="25"/>
       <c r="AG43" s="29" t="inlineStr">
         <is>
@@ -6259,7 +6241,7 @@
       <c r="AB44" s="24"/>
       <c r="AC44" s="24"/>
       <c r="AD44" s="30"/>
-      <c r="AE44" s="44"/>
+      <c r="AE44" s="43"/>
       <c r="AF44" s="25"/>
       <c r="AG44" s="29" t="inlineStr">
         <is>
@@ -6336,7 +6318,7 @@
       <c r="AB45" s="24"/>
       <c r="AC45" s="24"/>
       <c r="AD45" s="30"/>
-      <c r="AE45" s="44"/>
+      <c r="AE45" s="43"/>
       <c r="AF45" s="25"/>
       <c r="AG45" s="29" t="inlineStr">
         <is>
@@ -6413,7 +6395,7 @@
       <c r="AB46" s="24"/>
       <c r="AC46" s="24"/>
       <c r="AD46" s="30"/>
-      <c r="AE46" s="44"/>
+      <c r="AE46" s="43"/>
       <c r="AF46" s="25"/>
       <c r="AG46" s="29" t="inlineStr">
         <is>
@@ -6490,7 +6472,7 @@
       <c r="AB47" s="24"/>
       <c r="AC47" s="24"/>
       <c r="AD47" s="30"/>
-      <c r="AE47" s="44"/>
+      <c r="AE47" s="43"/>
       <c r="AF47" s="25"/>
       <c r="AG47" s="29" t="inlineStr">
         <is>
